--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-protocols-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-protocols-hard.xlsx
@@ -460,19 +460,19 @@
         <v>SPI là giao thức truyền dữ liệu chung, không có khái niệm chu kỳ thời gian thực cho audio frames. I2S là giao thức chuyên biệt cho âm thanh số, có 3 dây: SCK (xung nhịp bit), SD (dữ liệu), và WS (Word Select - xác định kênh Left/Right). WS giúp đồng bộ hóa chính xác tần số lấy mẫu (Sampling rate), triệt tiêu lỗi Jitter (lệch pha thời gian) gây rè hoặc mất tiếng của audio.</v>
       </c>
       <c r="F2" t="str">
-        <v>I2S có đường truyền xung nhịp clock chuyên biệt cho kênh âm thanh trái/phải (WS/LRCK) giúp đồng bộ hóa dữ liệu âm thanh chính xác tuyệt đối ở tần số lấy mẫu cố định, tránh hiện tượng lệch pha jitter — I2S đồng bộ hóa kênh âm thanh chuyên biệt</v>
+        <v>I2S tự động nén dữ liệu âm thanh sang định dạng file mp3 trước khi truyền về chip — tự động nén mp3</v>
       </c>
       <c r="G2" t="str">
         <v>SPI không hỗ trợ tốc độ truyền dẫn dữ liệu vượt quá 1 MHz — giới hạn tốc độ SPI</v>
       </c>
       <c r="H2" t="str">
-        <v>I2S tự động nén dữ liệu âm thanh sang định dạng file mp3 trước khi truyền về chip — tự động nén mp3</v>
+        <v>I2S có đường truyền xung nhịp clock chuyên biệt cho kênh âm thanh trái/phải (WS/LRCK) giúp đồng bộ hóa dữ liệu âm thanh chính xác tuyệt đối ở tần số lấy mẫu cố định, tránh hiện tượng lệch pha jitter — I2S đồng bộ hóa kênh âm thanh chuyên biệt</v>
       </c>
       <c r="I2" t="str">
         <v>I2S sử dụng tín hiệu vi sai giúp chống nhiễu tốt hơn SPI gấp 100 lần trên đường dây dài — so sánh chống nhiễu vi sai</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Bộ điều khiển CAN của mỗi nút tự động đếm lỗi (TEC và REC): Nếu lỗi liên tục vượt ngưỡng 255 (Transmit Error Counter &gt; 255), nút đó tự động ngắt kết nối vật lý khỏi bus (chuyển sang trạng thái Bus-off) để bảo vệ mạng — cơ chế tự động cô lập nút lỗi Bus-off</v>
       </c>
       <c r="G3" t="str">
+        <v>Tất cả các ECU khác sẽ tự động tăng điện áp truyền của mình lên mức 12V để đè bẹp Error Frames — tăng điện áp đè bẹp</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Đường dây bus CAN tự động kích hoạt một cầu chì nhiệt vật lý để ngắt kết nối nút bị chập — cầu chì nhiệt vật lý</v>
+      </c>
+      <c r="I3" t="str">
         <v>Master sẽ gửi lệnh ngắt nguồn điện cấp cho ECU bị lỗi đó thông qua mạng không dây Wi-Fi — tắt nguồn chéo chéo</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Tất cả các ECU khác sẽ tự động tăng điện áp truyền của mình lên mức 12V để đè bẹp Error Frames — tăng điện áp đè bẹp</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Đường dây bus CAN tự động kích hoạt một cầu chì nhiệt vật lý để ngắt kết nối nút bị chập — cầu chì nhiệt vật lý</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>Modbus RTU truyền dữ liệu nhị phân thô, bất kỳ byte nào cũng có thể trùng với các mã điều khiển. Do đó, nó sử dụng định thời (Timing) để phân tách khung. Một khoảng lặng trên đường truyền kéo dài ít nhất 3.5 ký tự (ví dụ khoảng 4ms ở baudrate 9600) được coi là dấu hiệu kết thúc frame. Nếu khoảng nghỉ giữa các byte trong 1 frame vượt quá 1.5 ký tự, thiết bị nhận sẽ coi là frame bị lỗi và hủy bỏ.</v>
       </c>
       <c r="F4" t="str">
+        <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 1 byte dữ liệu để giải phóng bộ nhớ đệm UART — giải phóng buffer</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Không cần thời gian nghỉ, các khung truyền có thể gửi liên tục gối đầu lên nhau để đạt hiệu năng tối đa — truyền liên tục</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Thời gian nghỉ cố định luôn luôn là 10 mili-giây đối với tất cả các tốc độ truyền — thời gian trễ cố định</v>
+      </c>
+      <c r="I4" t="str">
         <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 3.5 ký tự (3.5 character time); để các thiết bị nhận biết được điểm kết thúc của khung cũ và điểm bắt đầu của khung mới do Modbus RTU không có start/stop bytes đặc biệt — Silent Interval 3.5 character time phân tách khung</v>
       </c>
-      <c r="G4" t="str">
-        <v>Thời gian nghỉ cố định luôn luôn là 10 mili-giây đối với tất cả các tốc độ truyền — thời gian trễ cố định</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 1 byte dữ liệu để giải phóng bộ nhớ đệm UART — giải phóng buffer</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Không cần thời gian nghỉ, các khung truyền có thể gửi liên tục gối đầu lên nhau để đạt hiệu năng tối đa — truyền liên tục</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>Nguy hiểm vì điện áp 5V từ pull-up của cảm biến có thể bơm dòng ngược làm hỏng chân GPIO của vi điều khiển 3.3V; giải pháp là sử dụng mạch chuyển đổi mức logic hai chiều (Bidirectional Logic Level Shifter) dùng Transistor MOSFET — mạch chuyển đổi mức logic hai chiều MOSFET</v>
       </c>
       <c r="G5" t="str">
-        <v>Nguy hiểm vì cảm biến sẽ bị thiếu nguồn điện hoạt động và tự động sập nguồn; giải pháp là nối thêm một chiếc pin 9V vào mạch — nối pin phụ</v>
+        <v>Nguy hiểm vì tốc độ xung nhịp SCL của cảm biến sẽ bị giảm đi một nửa; giải pháp là tăng tần số thạch anh ngoại vi — tăng tần số thạch anh</v>
       </c>
       <c r="H5" t="str">
         <v>Giải pháp là lập trình viết code tăng điện áp đầu ra của chân GPIO vi điều khiển lên mức 5V — lập trình tăng điện áp GPIO</v>
       </c>
       <c r="I5" t="str">
-        <v>Nguy hiểm vì tốc độ xung nhịp SCL của cảm biến sẽ bị giảm đi một nửa; giải pháp là tăng tần số thạch anh ngoại vi — tăng tần số thạch anh</v>
+        <v>Nguy hiểm vì cảm biến sẽ bị thiếu nguồn điện hoạt động và tự động sập nguồn; giải pháp là nối thêm một chiếc pin 9V vào mạch — nối pin phụ</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>TCP có cơ chế bắt tay 3 bước (3-way handshake) và gửi lại gói tin bị mất (Automatic Repeat Request), tạo ra độ trễ (latency) không đoán trước được. UDP không duy trì kết nối, bắn gói tin đi ngay lập tức. Trong thu thập dữ liệu cảm biến thời gian thực (như đo góc máy bay), dữ liệu mới quan trọng nhất. Nếu mất gói tin cũ, việc gửi lại (của TCP) chỉ làm nghẽn băng thông và làm sai lệch thời gian thực của dữ liệu mới, do đó chọn UDP/IP.</v>
       </c>
       <c r="F6" t="str">
-        <v>TCP hướng kết nối, đảm bảo truyền tin cậy, sửa lỗi bằng cách gửi lại (retry - chậm hơn); UDP không kết nối, truyền nhanh, không đảm bảo sửa lỗi; chọn UDP khi cần truyền tốc độ cao dữ liệu cảm biến định kỳ liên tục, chấp nhận mất mát vài gói tin cũ — TCP tin cậy chậm vs UDP nhanh không kết nối thích hợp streaming dữ liệu cảm biến</v>
+        <v>TCP bắt buộc phải mã hóa dữ liệu bằng thuật toán AES; còn UDP hoàn toàn không hỗ trợ bảo mật — phân loại bảo mật</v>
       </c>
       <c r="G6" t="str">
         <v>TCP chỉ chạy được trên mạng cáp đồng; còn UDP chỉ chạy được trên mạng không dây Wi-Fi — phân loại môi trường truyền</v>
       </c>
       <c r="H6" t="str">
-        <v>TCP bắt buộc phải mã hóa dữ liệu bằng thuật toán AES; còn UDP hoàn toàn không hỗ trợ bảo mật — phân loại bảo mật</v>
+        <v>TCP hướng kết nối, đảm bảo truyền tin cậy, sửa lỗi bằng cách gửi lại (retry - chậm hơn); UDP không kết nối, truyền nhanh, không đảm bảo sửa lỗi; chọn UDP khi cần truyền tốc độ cao dữ liệu cảm biến định kỳ liên tục, chấp nhận mất mát vài gói tin cũ — TCP tin cậy chậm vs UDP nhanh không kết nối thích hợp streaming dữ liệu cảm biến</v>
       </c>
       <c r="I6" t="str">
         <v>TCP luôn luôn tiêu thụ năng lượng của chip ít hơn gấp 10 lần so với giao thức UDP — so sánh tiêu thụ điện năng</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>USB HID rất phổ biến cho các thiết bị điều khiển vì tính tiện lợi (Plug and Play), hệ điều hành Windows/Linux/Mac tích hợp sẵn driver chuẩn của nó. USB CDC (Virtual COM Port) yêu cầu cài đặt driver CDC (trên Windows cũ) và thích hợp để tạo giao diện dòng lệnh (CLI) gỡ lỗi hoặc truyền nhận file thô giữa MCU và PC.</v>
       </c>
       <c r="F7" t="str">
-        <v>HID dùng cho các thiết bị tương tác người dùng (chuột, bàn phím) chạy không cần cài đặt driver trên máy tính; CDC giả lập cổng COM ảo nối tiếp dùng để truyền nhận dữ liệu tự do — HID cắm chạy không driver vs CDC giả lập COM truyền dữ liệu tự do</v>
+        <v>HID bắt buộc phải sử dụng cáp kết nối USB-C; còn CDC chỉ hỗ trợ cổng USB Type-A cũ — loại cổng cắm vật lý</v>
       </c>
       <c r="G7" t="str">
         <v>HID chỉ hỗ trợ truyền dữ liệu tốc độ 115200 bps; còn CDC hỗ trợ tốc độ không giới hạn — so sánh tốc độ</v>
       </c>
       <c r="H7" t="str">
-        <v>HID bắt buộc phải sử dụng cáp kết nối USB-C; còn CDC chỉ hỗ trợ cổng USB Type-A cũ — loại cổng cắm vật lý</v>
+        <v>HID dùng cho các thiết bị tương tác người dùng (chuột, bàn phím) chạy không cần cài đặt driver trên máy tính; CDC giả lập cổng COM ảo nối tiếp dùng để truyền nhận dữ liệu tự do — HID cắm chạy không driver vs CDC giả lập COM truyền dữ liệu tự do</v>
       </c>
       <c r="I7" t="str">
         <v>HID chỉ dành cho hệ điều hành Windows; còn CDC chỉ dành riêng cho Linux — hệ điều hành hỗ trợ</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Chế độ Parasite Power (nguồn ký sinh) của 1-Wire cho phép chip sạc một tụ điện nội vi khi đường truyền ở mức High, và dùng năng lượng đó để hoạt động khi đường truyền kéo xuống Low để gửi dữ liệu. Nhờ đó, cảm biến chỉ cần 2 dây (1 dây Data/Power + 1 dây Ground) để hoạt động, giảm tối đa số lõi dây dẫn.</v>
       </c>
       <c r="F8" t="str">
+        <v>Truyền tín hiệu thông qua sóng vô tuyến hồng ngoại không cần dây dẫn vật lý — hồng ngoại không dây</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Bắt buộc phải sử dụng các sợi dây cáp đồng có đường kính lõi lớn hơn 5mm — đường kính dây dẫn lõi lớn</v>
+      </c>
+      <c r="H8" t="str">
         <v>Chỉ sử dụng duy nhất một dây tín hiệu chung cho cả việc cấp nguồn điện (Parasite Power mode) và truyền dữ liệu hai chiều, dùng chung dây GND — 1 dây tín hiệu kiêm cấp nguồn parasite power</v>
       </c>
-      <c r="G8" t="str">
-        <v>Truyền tín hiệu thông qua sóng vô tuyến hồng ngoại không cần dây dẫn vật lý — hồng ngoại không dây</v>
-      </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Tự động đồng bộ hóa dữ liệu thông qua đường dây điện xoay chiều 220V của nhà lưới — truyền tín hiệu qua đường điện lực</v>
       </c>
-      <c r="I8" t="str">
-        <v>Bắt buộc phải sử dụng các sợi dây cáp đồng có đường kính lõi lớn hơn 5mm — đường kính dây dẫn lõi lớn</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Tín hiệu vi sai truyền 2 dây ngược pha ($D+$ và $D-$). Nếu chiều dài 2 đường mạch trên PCB không bằng nhau (lệch pha Skew), sườn xung sẽ đến bộ thu lệch thời gian, triệt tiêu khả năng khử nhiễu đồng pha và gây méo dạng sóng. Không khớp trở kháng (thường thiết kế 90 Ohm cho USB, 100 Ohm cho Ethernet) sẽ gây phản xạ tín hiệu, làm tăng tỷ lệ lỗi bit (BER) ở tốc độ cao.</v>
       </c>
       <c r="F9" t="str">
+        <v>Để hệ điều hành của vi điều khiển tự động nâng tần số hoạt động của thạch anh lên gấp 10 lần — tăng tốc thạch anh</v>
+      </c>
+      <c r="G9" t="str">
         <v>Để tránh lệch pha thời gian (Skew) giữa hai tín hiệu vi sai gây méo mó dữ liệu và triệt tiêu tính chống nhiễu; trở kháng không khớp gây dội ngược tín hiệu phản xạ — cân bằng chiều dài và trở kháng đặc tính vi sai tốc độ cao</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Để đảm bảo dòng điện chạy qua hai dây dẫn luôn luôn bằng đúng 1 Ampe — dòng điện không đổi</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Để hệ điều hành của vi điều khiển tự động nâng tần số hoạt động của thạch anh lên gấp 10 lần — tăng tốc thạch anh</v>
       </c>
       <c r="I9" t="str">
         <v>Để ngăn chặn nước ẩm từ môi trường bên ngoài thấm vào bên trong mạch đồng — chống ẩm bảng mạch</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Modbus RTU sử dụng mã CRC16 ở cuối frame để kiểm tra toàn vẹn. Modbus TCP chạy trên giao thức mạng TCP/IP vốn đã có mã check checksum rất mạnh ở tầng vật lý/liên kết. Do đó, Modbus TCP bỏ CRC16 đi để giảm overhead, và thêm MBAP (Modbus Application Protocol) Header chứa Transaction ID, Protocol ID, Length và Unit ID để định tuyến qua mạng IP.</v>
       </c>
       <c r="F10" t="str">
+        <v>Modbus TCP chỉ hỗ trợ truyền dữ liệu một chiều từ Master sang Slave chứ không cho phép phản hồi — truyền một chiều</v>
+      </c>
+      <c r="G10" t="str">
         <v>Modbus TCP loại bỏ hoàn toàn trường kiểm tra lỗi CRC16 (vì tầng TCP/IP đã có cơ chế check lỗi toàn vẹn gói tin) và thêm mã nhận diện MBAP Header ở đầu khung — loại bỏ CRC16 thêm MBAP Header</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Modbus TCP bắt buộc phải sử dụng định dạng JSON để đóng gói dữ liệu truyền đi — định dạng JSON</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Modbus TCP chỉ hỗ trợ truyền dữ liệu một chiều từ Master sang Slave chứ không cho phép phản hồi — truyền một chiều</v>
       </c>
       <c r="I10" t="str">
         <v>Modbus TCP yêu cầu vi điều khiển phải chạy ở chế độ Sleep mode trong suốt quá trình truyền nhận — chế độ ngủ</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Ở tần số cao (20 MHz), đường mạch PCB đóng vai trò là một đường truyền sóng có điện dung ký sinh. Nếu dòng drive strength của chân GPIO quá yếu, tụ ký sinh sẽ nạp chậm làm sườn xung bị bo tròn (không còn dạng vuông), gây đọc sai bit. Tăng drive strength giúp sườn xung vuông vắn. Tuy nhiên, nếu sườn quá dốc sẽ gây hiện tượng quá đà (Overshoot)/dưới đà (Undershoot), cần điều chỉnh Slew Rate thích hợp để bảo vệ toàn vẹn tín hiệu.</v>
       </c>
       <c r="F11" t="str">
-        <v>Cấu hình tăng dòng kích thích (Drive Strength) của chân GPIO phát, giảm tốc độ sườn xung (Slew Rate control) hợp lý, và thiết kế đường mạch ngắn nhất có thể — cấu hình dòng kích thích GPIO drive strength</v>
+        <v>Lập trình viết code tự động nhả chân CS sau mỗi 1 byte dữ liệu truyền đi — nhả CS liên tục làm giảm hiệu năng</v>
       </c>
       <c r="G11" t="str">
         <v>Mắc song song một con tụ điện dung lượng lớn 100uF vào chân tín hiệu clock SCK xuống đất — tụ lọc nhiễu lớn làm sập sườn xung</v>
       </c>
       <c r="H11" t="str">
-        <v>Lập trình viết code tự động nhả chân CS sau mỗi 1 byte dữ liệu truyền đi — nhả CS liên tục làm giảm hiệu năng</v>
+        <v>Thay thế toàn bộ vi điều khiển bằng một con chip RF không dây Bluetooth — giải pháp không dây không liên quan</v>
       </c>
       <c r="I11" t="str">
-        <v>Thay thế toàn bộ vi điều khiển bằng một con chip RF không dây Bluetooth — giải pháp không dây không liên quan</v>
+        <v>Cấu hình tăng dòng kích thích (Drive Strength) của chân GPIO phát, giảm tốc độ sườn xung (Slew Rate control) hợp lý, và thiết kế đường mạch ngắn nhất có thể — cấu hình dòng kích thích GPIO drive strength</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
